--- a/marketing_forms/040_marketing_brief_form_template--marketing_forms.xlsx
+++ b/marketing_forms/040_marketing_brief_form_template--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>marketing_brief</t>
+          <t>Marketing Brief</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>marketing_goal</t>
+          <t>Marketing Goal</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,10 +571,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>marketing_objectives</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Marketing Objectives</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>List the specific objectives of the campaign.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,23 +588,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>marketing_strategy</t>
+          <t>marketing_channels</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>marketing_strategy</t>
+          <t>Marketing Channels</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,7 +621,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>target_audience</t>
+          <t>Target Audience</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,23 +634,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>marketing_channels</t>
+          <t>marketing_strategy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>marketing_channels</t>
+          <t>Marketing Strategy</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -663,7 +667,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>marketing_budget</t>
+          <t>Marketing Budget</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +690,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>marketing_duration</t>
+          <t>Marketing Duration</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +713,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>marketing_start_date</t>
+          <t>Marketing Start Date</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +736,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>marketing_end_date</t>
+          <t>Marketing End Date</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +759,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>marketing_frequency</t>
+          <t>Marketing Frequency</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +782,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>marketing_status</t>
+          <t>Marketing Status</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +805,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>Assigned To</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +828,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>Submitted By</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +851,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>submitted_date</t>
+          <t>Submitted Date</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +874,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>submitted_time</t>
+          <t>Submitted Time</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +897,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +915,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>assigned_notes</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>assigned_notes</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>submitted_notes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>submitted_notes</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>status_comments</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>status_comments</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>assigned_by</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>assigned_by</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>submitted_date</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>submitted_date</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>submitted_time</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>submitted_time</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>assigned_by</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>assigned_by</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +941,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +974,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -1148,78 +991,180 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>email_marketing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Email Marketing</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>marketing_frequency_choices</t>
+          <t>marketing_channels_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>print_media</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Print Media</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>marketing_frequency_choices</t>
+          <t>marketing_channels_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>online_advertising</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Online Advertising</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>marketing_status_choices</t>
+          <t>marketing_channels_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>influencer_marketing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Influencer Marketing</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>marketing_channels_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>event_marketing</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Event Marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>marketing_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>marketing_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>marketing_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>bi-weekly</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bi-Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>marketing_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>marketing_status_choices</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>marketing_status_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>inactive</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
